--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167918</v>
+        <v>125167932</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881167</v>
+        <v>881215</v>
       </c>
       <c r="R2" t="n">
-        <v>7392770</v>
+        <v>7392847</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167932</v>
+        <v>125167930</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881215</v>
+        <v>881276</v>
       </c>
       <c r="R3" t="n">
-        <v>7392847</v>
+        <v>7392828</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167930</v>
+        <v>125167918</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881276</v>
+        <v>881167</v>
       </c>
       <c r="R4" t="n">
-        <v>7392828</v>
+        <v>7392770</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167932</v>
+        <v>125167918</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881215</v>
+        <v>881167</v>
       </c>
       <c r="R2" t="n">
-        <v>7392847</v>
+        <v>7392770</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167918</v>
+        <v>125167932</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881167</v>
+        <v>881215</v>
       </c>
       <c r="R4" t="n">
-        <v>7392770</v>
+        <v>7392847</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167918</v>
+        <v>125167930</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881167</v>
+        <v>881276</v>
       </c>
       <c r="R2" t="n">
-        <v>7392770</v>
+        <v>7392828</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167930</v>
+        <v>125167932</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881276</v>
+        <v>881215</v>
       </c>
       <c r="R3" t="n">
-        <v>7392828</v>
+        <v>7392847</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167932</v>
+        <v>125167918</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881215</v>
+        <v>881167</v>
       </c>
       <c r="R4" t="n">
-        <v>7392847</v>
+        <v>7392770</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167930</v>
+        <v>125167918</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881276</v>
+        <v>881167</v>
       </c>
       <c r="R2" t="n">
-        <v>7392828</v>
+        <v>7392770</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +785,7 @@
         <v>125167932</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167918</v>
+        <v>125167930</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881167</v>
+        <v>881276</v>
       </c>
       <c r="R4" t="n">
-        <v>7392770</v>
+        <v>7392828</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -984,6 +984,210 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125616389</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hiirivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>881341</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7392835</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125616391</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hiirivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>881167</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7392789</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167918</v>
+        <v>125167932</v>
       </c>
       <c r="B2" t="n">
-        <v>56836</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881167</v>
+        <v>881215</v>
       </c>
       <c r="R2" t="n">
-        <v>7392770</v>
+        <v>7392847</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167932</v>
+        <v>125167930</v>
       </c>
       <c r="B3" t="n">
         <v>98269</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881215</v>
+        <v>881276</v>
       </c>
       <c r="R3" t="n">
-        <v>7392847</v>
+        <v>7392828</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167930</v>
+        <v>125167918</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881276</v>
+        <v>881167</v>
       </c>
       <c r="R4" t="n">
-        <v>7392828</v>
+        <v>7392770</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167932</v>
+        <v>125167930</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881215</v>
+        <v>881276</v>
       </c>
       <c r="R2" t="n">
-        <v>7392847</v>
+        <v>7392828</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167930</v>
+        <v>125167932</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881276</v>
+        <v>881215</v>
       </c>
       <c r="R3" t="n">
-        <v>7392828</v>
+        <v>7392847</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -882,12 +872,7 @@
         <v>125167918</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125616389</v>
+        <v>125616391</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881341</v>
+        <v>881167</v>
       </c>
       <c r="R5" t="n">
-        <v>7392835</v>
+        <v>7392789</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125616391</v>
+        <v>125616389</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881167</v>
+        <v>881341</v>
       </c>
       <c r="R6" t="n">
-        <v>7392789</v>
+        <v>7392835</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125167930</v>
       </c>
       <c r="B2" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125167932</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125616391</v>
       </c>
       <c r="B5" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125616389</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125616391</v>
       </c>
       <c r="B5" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125616389</v>
       </c>
       <c r="B6" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125616391</v>
       </c>
       <c r="B5" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125616389</v>
       </c>
       <c r="B6" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125616391</v>
       </c>
       <c r="B5" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125616389</v>
       </c>
       <c r="B6" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125616391</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125616389</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125616391</v>
       </c>
       <c r="B5" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125616389</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>125616391</v>
       </c>
       <c r="B5" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125616389</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1163,6 +1163,1914 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128533221</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>881206</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7392806</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128533224</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>881218</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7392820</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128533225</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>881243</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7392864</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128533233</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>881341</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7392851</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128533236</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>881345</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7392843</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128533229</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>881318</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7392862</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128533231</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>881328</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7392857</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128533219</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>881220</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7392796</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128533222</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>881227</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7392822</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128533226</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>881258</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7392829</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128533228</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>881280</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7392858</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128533220</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>881216</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7392799</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128533232</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>881329</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7392852</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128533210</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>881275</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7392829</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128533235</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>881334</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7392849</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128533230</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>881299</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7392849</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128533223</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>881219</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7392835</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128533227</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>881255</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7392857</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -1271,7 +1271,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128533224</v>
+        <v>128533225</v>
       </c>
       <c r="B8" t="n">
         <v>98571</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881218</v>
+        <v>881243</v>
       </c>
       <c r="R8" t="n">
-        <v>7392820</v>
+        <v>7392864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128533225</v>
+        <v>128533224</v>
       </c>
       <c r="B9" t="n">
         <v>98571</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881243</v>
+        <v>881218</v>
       </c>
       <c r="R9" t="n">
-        <v>7392864</v>
+        <v>7392820</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128533236</v>
+        <v>128533229</v>
       </c>
       <c r="B11" t="n">
         <v>98571</v>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>881345</v>
+        <v>881318</v>
       </c>
       <c r="R11" t="n">
-        <v>7392843</v>
+        <v>7392862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128533229</v>
+        <v>128533236</v>
       </c>
       <c r="B12" t="n">
         <v>98571</v>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>881318</v>
+        <v>881345</v>
       </c>
       <c r="R12" t="n">
-        <v>7392862</v>
+        <v>7392843</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128533231</v>
+        <v>128533219</v>
       </c>
       <c r="B13" t="n">
         <v>98571</v>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>881328</v>
+        <v>881220</v>
       </c>
       <c r="R13" t="n">
-        <v>7392857</v>
+        <v>7392796</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128533219</v>
+        <v>128533231</v>
       </c>
       <c r="B14" t="n">
         <v>98571</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>881220</v>
+        <v>881328</v>
       </c>
       <c r="R14" t="n">
-        <v>7392796</v>
+        <v>7392857</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,7 +2119,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128533226</v>
+        <v>128533228</v>
       </c>
       <c r="B16" t="n">
         <v>98571</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>881258</v>
+        <v>881280</v>
       </c>
       <c r="R16" t="n">
-        <v>7392829</v>
+        <v>7392858</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128533228</v>
+        <v>128533226</v>
       </c>
       <c r="B17" t="n">
         <v>98571</v>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>881280</v>
+        <v>881258</v>
       </c>
       <c r="R17" t="n">
-        <v>7392858</v>
+        <v>7392829</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533235</v>
+        <v>128533230</v>
       </c>
       <c r="B21" t="n">
         <v>98571</v>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>881334</v>
+        <v>881299</v>
       </c>
       <c r="R21" t="n">
         <v>7392849</v>
@@ -2755,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128533230</v>
+        <v>128533235</v>
       </c>
       <c r="B22" t="n">
         <v>98571</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>881299</v>
+        <v>881334</v>
       </c>
       <c r="R22" t="n">
         <v>7392849</v>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -2649,7 +2649,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533230</v>
+        <v>128533235</v>
       </c>
       <c r="B21" t="n">
         <v>98571</v>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>881299</v>
+        <v>881334</v>
       </c>
       <c r="R21" t="n">
         <v>7392849</v>
@@ -2755,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128533235</v>
+        <v>128533230</v>
       </c>
       <c r="B22" t="n">
         <v>98571</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>881334</v>
+        <v>881299</v>
       </c>
       <c r="R22" t="n">
         <v>7392849</v>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>128533221</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128533225</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128533224</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128533233</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128533229</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128533236</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>128533219</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>128533231</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128533222</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>128533228</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128533226</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>128533220</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128533232</v>
+        <v>128533210</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>881329</v>
+        <v>881275</v>
       </c>
       <c r="R19" t="n">
-        <v>7392852</v>
+        <v>7392829</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128533210</v>
+        <v>128533232</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>881275</v>
+        <v>881329</v>
       </c>
       <c r="R20" t="n">
-        <v>7392829</v>
+        <v>7392852</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533235</v>
+        <v>128533230</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>881334</v>
+        <v>881299</v>
       </c>
       <c r="R21" t="n">
         <v>7392849</v>
@@ -2755,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128533230</v>
+        <v>128533235</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>881299</v>
+        <v>881334</v>
       </c>
       <c r="R22" t="n">
         <v>7392849</v>
@@ -2864,7 +2864,7 @@
         <v>128533223</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>128533227</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>128533221</v>
       </c>
       <c r="B7" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128533225</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128533224</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128533233</v>
       </c>
       <c r="B10" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128533229</v>
       </c>
       <c r="B11" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128533236</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>128533219</v>
       </c>
       <c r="B13" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>128533231</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128533222</v>
       </c>
       <c r="B15" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>128533228</v>
       </c>
       <c r="B16" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128533226</v>
       </c>
       <c r="B17" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>128533220</v>
       </c>
       <c r="B18" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128533210</v>
       </c>
       <c r="B19" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>128533232</v>
       </c>
       <c r="B20" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>128533230</v>
       </c>
       <c r="B21" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>128533235</v>
       </c>
       <c r="B22" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128533223</v>
       </c>
       <c r="B23" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>128533227</v>
       </c>
       <c r="B24" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>128533221</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128533225</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128533224</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128533233</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128533229</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128533236</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>128533219</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>128533231</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128533222</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>128533228</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128533226</v>
       </c>
       <c r="B17" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>128533220</v>
       </c>
       <c r="B18" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128533210</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>128533232</v>
       </c>
       <c r="B20" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>128533230</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>128533235</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>128533223</v>
       </c>
       <c r="B23" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>128533227</v>
       </c>
       <c r="B24" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>128533221</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128533225</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>128533224</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128533233</v>
       </c>
       <c r="B10" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>128533229</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128533236</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>128533219</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>128533231</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>128533222</v>
       </c>
       <c r="B15" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>128533228</v>
       </c>
       <c r="B16" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>128533226</v>
       </c>
       <c r="B17" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>128533220</v>
       </c>
       <c r="B18" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>128533210</v>
       </c>
       <c r="B19" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>128533232</v>
       </c>
       <c r="B20" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533230</v>
+        <v>128533235</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>881299</v>
+        <v>881334</v>
       </c>
       <c r="R21" t="n">
         <v>7392849</v>
@@ -2755,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128533235</v>
+        <v>128533230</v>
       </c>
       <c r="B22" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>881334</v>
+        <v>881299</v>
       </c>
       <c r="R22" t="n">
         <v>7392849</v>
@@ -2864,7 +2864,7 @@
         <v>128533223</v>
       </c>
       <c r="B23" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>128533227</v>
       </c>
       <c r="B24" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 15494-2022 artfynd.xlsx
+++ b/artfynd/A 15494-2022 artfynd.xlsx
@@ -2013,7 +2013,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128533222</v>
+        <v>128533228</v>
       </c>
       <c r="B15" t="n">
         <v>98591</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>881227</v>
+        <v>881280</v>
       </c>
       <c r="R15" t="n">
-        <v>7392822</v>
+        <v>7392858</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,7 +2119,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128533228</v>
+        <v>128533226</v>
       </c>
       <c r="B16" t="n">
         <v>98591</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>881280</v>
+        <v>881258</v>
       </c>
       <c r="R16" t="n">
-        <v>7392858</v>
+        <v>7392829</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128533226</v>
+        <v>128533222</v>
       </c>
       <c r="B17" t="n">
         <v>98591</v>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>881258</v>
+        <v>881227</v>
       </c>
       <c r="R17" t="n">
-        <v>7392829</v>
+        <v>7392822</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
